--- a/Arquivos/bases_apoio/tab_de-para.xlsx
+++ b/Arquivos/bases_apoio/tab_de-para.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.20\ddmrj-dados\Planejamento\FIRJAN\Dashboard\dashboard-firjan\Arquivos\bases_apoio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F8EDFA-3C6A-4043-A308-4AC5551D9300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177D6F3D-68EA-4DEC-9AD8-853C5AFD481B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="status" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="138">
   <si>
     <t>Unidade</t>
   </si>
@@ -432,6 +432,12 @@
   </si>
   <si>
     <t>MATRICULA ONLINE</t>
+  </si>
+  <si>
+    <t>Matrícula realizada</t>
+  </si>
+  <si>
+    <t>Comparecerá na unidade</t>
   </si>
 </sst>
 </file>
@@ -542,9 +548,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -582,7 +588,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -688,7 +694,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -830,7 +836,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -838,11 +844,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:B33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1090,6 +1096,22 @@
         <v>135</v>
       </c>
       <c r="B31" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>136</v>
+      </c>
+      <c r="B32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>137</v>
+      </c>
+      <c r="B33" t="s">
         <v>104</v>
       </c>
     </row>
@@ -1102,11 +1124,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B97"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
